--- a/Excel/Story.xlsx
+++ b/Excel/Story.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80862954-EF1F-45B2-A29F-3C2E25FDC971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3666725-F933-477D-90E0-45F413816035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Story" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,43 @@
   <si>
     <t>track</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dictionary&lt;int,string&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|4,yyy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|5,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|6,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|7,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|8,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|9,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|10,yyy</t>
+  </si>
+  <si>
+    <t>1,sss|2,ddd|3,fff|11,yyy</t>
   </si>
 </sst>
 </file>
@@ -415,17 +452,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="4" width="14.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="19.5" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,8 +479,11 @@
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -458,8 +499,11 @@
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -472,8 +516,11 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -486,8 +533,11 @@
       <c r="E5" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -500,8 +550,11 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -514,8 +567,11 @@
       <c r="E7" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -528,8 +584,11 @@
       <c r="E8" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -542,8 +601,11 @@
       <c r="E9" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -556,8 +618,11 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -567,8 +632,11 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -578,8 +646,11 @@
       <c r="E12" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -590,7 +661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -601,7 +672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -612,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>12</v>
       </c>
